--- a/templates/coach_availability_template.xlsx
+++ b/templates/coach_availability_template.xlsx
@@ -436,14 +436,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,20 +455,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coach ID</t>
+          <t>Coach SF ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Coach Email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>End Time</t>
         </is>
@@ -476,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t># Legend: one row per weekly availability block per coach. Coach Name must be spelled identically on every row for the same coach. Coach ID optional (carried into the export). Times in 24-hour HH:MM. Rows starting with # are ignored.</t>
+          <t># Legend: one row per weekly availability block per coach. Every column is required. Coach Name, Coach SF ID and Coach Email must be spelled identically on every row for the same coach. Day = Monday–Sunday (or Mon/Tue...). Times in 24-hour HH:MM, in the campus local time you selected in the app. Rows starting with # are ignored.</t>
         </is>
       </c>
     </row>
@@ -493,15 +499,20 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>alex.coach@example.com</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
